--- a/output/region_summary.xlsx
+++ b/output/region_summary.xlsx
@@ -441,65 +441,65 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>West</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>378.5</v>
+        <v>440</v>
       </c>
       <c r="D2" t="n">
-        <v>94.625</v>
+        <v>440</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>North</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>575</v>
+        <v>378.5</v>
       </c>
       <c r="D3" t="n">
-        <v>191.6666666666667</v>
+        <v>94.625</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>East</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>275</v>
+        <v>575</v>
       </c>
       <c r="D4" t="n">
-        <v>137.5</v>
+        <v>191.6666666666667</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>South</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>440</v>
+        <v>275</v>
       </c>
       <c r="D5" t="n">
-        <v>440</v>
+        <v>137.5</v>
       </c>
     </row>
   </sheetData>

--- a/output/region_summary.xlsx
+++ b/output/region_summary.xlsx
@@ -480,10 +480,10 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>575</v>
+        <v>595.5</v>
       </c>
       <c r="D4" t="n">
-        <v>191.6666666666667</v>
+        <v>297.75</v>
       </c>
     </row>
     <row r="5">

--- a/output/region_summary.xlsx
+++ b/output/region_summary.xlsx
@@ -441,49 +441,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>North</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>440</v>
+        <v>378.5</v>
       </c>
       <c r="D2" t="n">
-        <v>440</v>
+        <v>94.625</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>East</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" t="n">
-        <v>378.5</v>
+        <v>660.5</v>
       </c>
       <c r="D3" t="n">
-        <v>94.625</v>
+        <v>220.1666666666667</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>West</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>595.5</v>
+        <v>440</v>
       </c>
       <c r="D4" t="n">
-        <v>297.75</v>
+        <v>440</v>
       </c>
     </row>
     <row r="5">

--- a/output/region_summary.xlsx
+++ b/output/region_summary.xlsx
@@ -441,17 +441,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>West</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>378.5</v>
+        <v>440</v>
       </c>
       <c r="D2" t="n">
-        <v>94.625</v>
+        <v>440</v>
       </c>
     </row>
     <row r="3">
@@ -473,17 +473,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>West</t>
+          <t>North</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>440</v>
+        <v>378.5</v>
       </c>
       <c r="D4" t="n">
-        <v>440</v>
+        <v>94.625</v>
       </c>
     </row>
     <row r="5">
